--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/ARIZONA_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/ARIZONA_2017.xlsx
@@ -5748,7 +5748,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C300">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C749">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C750">
